--- a/Seção 6/89.0PROCV+exemplo+3.xlsx
+++ b/Seção 6/89.0PROCV+exemplo+3.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://enelcom-my.sharepoint.com/personal/felipe_viana2_enel_com/Documents/Documentos/Faculdade/Udemy/Excell/Seção 6/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://enelcom-my.sharepoint.com/personal/felipe_viana2_enel_com/Documents/Documentos/Faculdade/Udemy/Excell/excel-data-analytics-portfolio/Seção 6/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{D7519AEE-1260-4B57-816E-6C40C2F0467D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ECD43C86-A81D-4652-8EF3-76D9F52CC7EB}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="13_ncr:1_{D7519AEE-1260-4B57-816E-6C40C2F0467D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65A5B905-1DE5-43F5-94A3-32F9073CFD0F}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="809" activeTab="1" xr2:uid="{2E65B82F-5866-47B8-BB74-66991D6C79DA}"/>
   </bookViews>
@@ -621,6 +621,10 @@
     </sheetDataSet>
   </externalBook>
 </externalLink>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1198,15 +1202,15 @@
         <v>2</v>
       </c>
       <c r="B2" s="5" t="str">
-        <f>VLOOKUP($A2,[2]Dados!$A:$D,2,0)</f>
+        <f>VLOOKUP(A2,[2]Dados!$A$1:$B$13,2,0)</f>
         <v>Bruna Alves</v>
       </c>
       <c r="C2" s="5">
-        <f>VLOOKUP($A2,[2]Dados!$A:$D,3,0)</f>
+        <f>VLOOKUP(A2,[2]Dados!$A$1:$D$13,3,0)</f>
         <v>23</v>
       </c>
       <c r="D2" s="5">
-        <f>VLOOKUP($A2,[2]Dados!$A:$D,4,0)</f>
+        <f>VLOOKUP(A2,[2]Dados!$A$1:$D$13,4,0)</f>
         <v>2000</v>
       </c>
     </row>
@@ -1215,15 +1219,15 @@
         <v>3</v>
       </c>
       <c r="B3" s="5" t="str">
-        <f>VLOOKUP($A3,[2]Dados!$A:$D,2,0)</f>
+        <f>VLOOKUP(A3,[2]Dados!$A$1:$B$13,2,0)</f>
         <v>Afonso Alves</v>
       </c>
       <c r="C3" s="5">
-        <f>VLOOKUP($A3,[2]Dados!$A:$D,3,0)</f>
+        <f>VLOOKUP(A3,[2]Dados!$A$1:$D$13,3,0)</f>
         <v>23</v>
       </c>
       <c r="D3" s="5">
-        <f>VLOOKUP($A3,[2]Dados!$A:$D,4,0)</f>
+        <f>VLOOKUP(A3,[2]Dados!$A$1:$D$13,4,0)</f>
         <v>2500</v>
       </c>
     </row>
@@ -1232,15 +1236,15 @@
         <v>4</v>
       </c>
       <c r="B4" s="5" t="str">
-        <f>VLOOKUP($A4,[2]Dados!$A:$D,2,0)</f>
+        <f>VLOOKUP(A4,[2]Dados!$A$1:$B$13,2,0)</f>
         <v>Caroline Gois Abreu</v>
       </c>
       <c r="C4" s="5">
-        <f>VLOOKUP($A4,[2]Dados!$A:$D,3,0)</f>
+        <f>VLOOKUP(A4,[2]Dados!$A$1:$D$13,3,0)</f>
         <v>50</v>
       </c>
       <c r="D4" s="5">
-        <f>VLOOKUP($A4,[2]Dados!$A:$D,4,0)</f>
+        <f>VLOOKUP(A4,[2]Dados!$A$1:$D$13,4,0)</f>
         <v>3000</v>
       </c>
     </row>
@@ -1249,15 +1253,15 @@
         <v>5</v>
       </c>
       <c r="B5" s="5" t="str">
-        <f>VLOOKUP($A5,[2]Dados!$A:$D,2,0)</f>
+        <f>VLOOKUP(A5,[2]Dados!$A$1:$B$13,2,0)</f>
         <v>Henrique Oliveira Silva</v>
       </c>
       <c r="C5" s="5">
-        <f>VLOOKUP($A5,[2]Dados!$A:$D,3,0)</f>
+        <f>VLOOKUP(A5,[2]Dados!$A$1:$D$13,3,0)</f>
         <v>26</v>
       </c>
       <c r="D5" s="5">
-        <f>VLOOKUP($A5,[2]Dados!$A:$D,4,0)</f>
+        <f>VLOOKUP(A5,[2]Dados!$A$1:$D$13,4,0)</f>
         <v>3000</v>
       </c>
     </row>
@@ -1266,15 +1270,15 @@
         <v>6</v>
       </c>
       <c r="B6" s="5" t="str">
-        <f>VLOOKUP($A6,[2]Dados!$A:$D,2,0)</f>
+        <f>VLOOKUP(A6,[2]Dados!$A$1:$B$13,2,0)</f>
         <v>Kaliane Almeida Abreu</v>
       </c>
       <c r="C6" s="5">
-        <f>VLOOKUP($A6,[2]Dados!$A:$D,3,0)</f>
+        <f>VLOOKUP(A6,[2]Dados!$A$1:$D$13,3,0)</f>
         <v>26</v>
       </c>
       <c r="D6" s="5">
-        <f>VLOOKUP($A6,[2]Dados!$A:$D,4,0)</f>
+        <f>VLOOKUP(A6,[2]Dados!$A$1:$D$13,4,0)</f>
         <v>2000</v>
       </c>
     </row>
@@ -1283,15 +1287,15 @@
         <v>7</v>
       </c>
       <c r="B7" s="5" t="str">
-        <f>VLOOKUP($A7,[2]Dados!$A:$D,2,0)</f>
+        <f>VLOOKUP(A7,[2]Dados!$A$1:$B$13,2,0)</f>
         <v>Ryan Merryman</v>
       </c>
       <c r="C7" s="5">
-        <f>VLOOKUP($A7,[2]Dados!$A:$D,3,0)</f>
+        <f>VLOOKUP(A7,[2]Dados!$A$1:$D$13,3,0)</f>
         <v>26</v>
       </c>
       <c r="D7" s="5">
-        <f>VLOOKUP($A7,[2]Dados!$A:$D,4,0)</f>
+        <f>VLOOKUP(A7,[2]Dados!$A$1:$D$13,4,0)</f>
         <v>2000</v>
       </c>
     </row>
@@ -1300,15 +1304,15 @@
         <v>8</v>
       </c>
       <c r="B8" s="5" t="str">
-        <f>VLOOKUP($A8,[2]Dados!$A:$D,2,0)</f>
+        <f>VLOOKUP(A8,[2]Dados!$A$1:$B$13,2,0)</f>
         <v>Robson Martins</v>
       </c>
       <c r="C8" s="5">
-        <f>VLOOKUP($A8,[2]Dados!$A:$D,3,0)</f>
+        <f>VLOOKUP(A8,[2]Dados!$A$1:$D$13,3,0)</f>
         <v>23</v>
       </c>
       <c r="D8" s="5">
-        <f>VLOOKUP($A8,[2]Dados!$A:$D,4,0)</f>
+        <f>VLOOKUP(A8,[2]Dados!$A$1:$D$13,4,0)</f>
         <v>2000</v>
       </c>
     </row>
@@ -1317,15 +1321,15 @@
         <v>9</v>
       </c>
       <c r="B9" s="5" t="str">
-        <f>VLOOKUP($A9,[2]Dados!$A:$D,2,0)</f>
+        <f>VLOOKUP(A9,[2]Dados!$A$1:$B$13,2,0)</f>
         <v>Thiago Santana Gomes</v>
       </c>
       <c r="C9" s="5">
-        <f>VLOOKUP($A9,[2]Dados!$A:$D,3,0)</f>
+        <f>VLOOKUP(A9,[2]Dados!$A$1:$D$13,3,0)</f>
         <v>30</v>
       </c>
       <c r="D9" s="5">
-        <f>VLOOKUP($A9,[2]Dados!$A:$D,4,0)</f>
+        <f>VLOOKUP(A9,[2]Dados!$A$1:$D$13,4,0)</f>
         <v>5000</v>
       </c>
     </row>
@@ -1334,15 +1338,15 @@
         <v>10</v>
       </c>
       <c r="B10" s="5" t="str">
-        <f>VLOOKUP($A10,[2]Dados!$A:$D,2,0)</f>
+        <f>VLOOKUP(A10,[2]Dados!$A$1:$B$13,2,0)</f>
         <v>Erika Souza Aguiar</v>
       </c>
       <c r="C10" s="5">
-        <f>VLOOKUP($A10,[2]Dados!$A:$D,3,0)</f>
+        <f>VLOOKUP(A10,[2]Dados!$A$1:$D$13,3,0)</f>
         <v>30</v>
       </c>
       <c r="D10" s="5">
-        <f>VLOOKUP($A10,[2]Dados!$A:$D,4,0)</f>
+        <f>VLOOKUP(A10,[2]Dados!$A$1:$D$13,4,0)</f>
         <v>5000</v>
       </c>
     </row>
@@ -1351,15 +1355,15 @@
         <v>11</v>
       </c>
       <c r="B11" s="5" t="str">
-        <f>VLOOKUP($A11,[2]Dados!$A:$D,2,0)</f>
+        <f>VLOOKUP(A11,[2]Dados!$A$1:$B$13,2,0)</f>
         <v>Felipe Borges Aguiar</v>
       </c>
       <c r="C11" s="5">
-        <f>VLOOKUP($A11,[2]Dados!$A:$D,3,0)</f>
+        <f>VLOOKUP(A11,[2]Dados!$A$1:$D$13,3,0)</f>
         <v>30</v>
       </c>
       <c r="D11" s="5">
-        <f>VLOOKUP($A11,[2]Dados!$A:$D,4,0)</f>
+        <f>VLOOKUP(A11,[2]Dados!$A$1:$D$13,4,0)</f>
         <v>5000</v>
       </c>
     </row>
@@ -1368,15 +1372,15 @@
         <v>12</v>
       </c>
       <c r="B12" s="5" t="str">
-        <f>VLOOKUP($A12,[2]Dados!$A:$D,2,0)</f>
+        <f>VLOOKUP(A12,[2]Dados!$A$1:$B$13,2,0)</f>
         <v>Tiago de Oliveira</v>
       </c>
       <c r="C12" s="5">
-        <f>VLOOKUP($A12,[2]Dados!$A:$D,3,0)</f>
+        <f>VLOOKUP(A12,[2]Dados!$A$1:$D$13,3,0)</f>
         <v>30</v>
       </c>
       <c r="D12" s="5">
-        <f>VLOOKUP($A12,[2]Dados!$A:$D,4,0)</f>
+        <f>VLOOKUP(A12,[2]Dados!$A$1:$D$13,4,0)</f>
         <v>4000</v>
       </c>
     </row>
@@ -1385,15 +1389,15 @@
         <v>13</v>
       </c>
       <c r="B13" s="5" t="str">
-        <f>VLOOKUP($A13,[2]Dados!$A:$D,2,0)</f>
+        <f>VLOOKUP(A13,[2]Dados!$A$1:$B$13,2,0)</f>
         <v>Frederico Rubens</v>
       </c>
       <c r="C13" s="5">
-        <f>VLOOKUP($A13,[2]Dados!$A:$D,3,0)</f>
+        <f>VLOOKUP(A13,[2]Dados!$A$1:$D$13,3,0)</f>
         <v>30</v>
       </c>
       <c r="D13" s="5">
-        <f>VLOOKUP($A13,[2]Dados!$A:$D,4,0)</f>
+        <f>VLOOKUP(A13,[2]Dados!$A$1:$D$13,4,0)</f>
         <v>4000</v>
       </c>
     </row>
@@ -1406,18 +1410,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1618,14 +1622,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8981F02B-5252-40A8-85C9-6E028D5DC5D2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{266DECCE-BB42-4B71-9D6C-EC24543CD393}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
@@ -1638,6 +1634,14 @@
     <ds:schemaRef ds:uri="fd550b8b-0dd7-4de3-a8e6-af527f15a8ac"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8981F02B-5252-40A8-85C9-6E028D5DC5D2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
